--- a/archivos/seguimiento.xlsx
+++ b/archivos/seguimiento.xlsx
@@ -6056,7 +6056,7 @@
         <v>49.7</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F153" s="7" t="n"/>
     </row>
@@ -6300,13 +6300,9 @@
         <v>47.6</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>149</v>
-      </c>
-      <c r="F164" s="7" t="inlineStr">
-        <is>
-          <t>Revisar talla: baja de 149 cm (feb) a 147 (jun) y 146 (sep)</t>
-        </is>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="F164" s="7" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
@@ -6770,7 +6766,7 @@
         <v>51</v>
       </c>
       <c r="E185" s="11" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F185" s="7" t="n"/>
     </row>
@@ -7062,7 +7058,7 @@
         <v>46.2</v>
       </c>
       <c r="E198" s="11" t="n">
-        <v>146</v>
+        <v>145.5</v>
       </c>
       <c r="F198" s="7" t="n"/>
     </row>
@@ -7550,7 +7546,7 @@
         <v>50.7</v>
       </c>
       <c r="E220" s="11" t="n">
-        <v>147.5</v>
+        <v>149</v>
       </c>
       <c r="F220" s="7" t="n"/>
     </row>
@@ -7730,7 +7726,7 @@
         <v>48.9</v>
       </c>
       <c r="E228" s="11" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F228" s="7" t="n"/>
     </row>
@@ -7774,7 +7770,7 @@
         <v>47.2</v>
       </c>
       <c r="E230" s="11" t="n">
-        <v>145.5</v>
+        <v>146</v>
       </c>
       <c r="F230" s="7" t="n"/>
     </row>
